--- a/fomo_two_papers/deliverables/paper2/Paper2_Data.xlsx
+++ b/fomo_two_papers/deliverables/paper2/Paper2_Data.xlsx
@@ -839,7 +839,7 @@
         <v>3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK2" t="n">
         <v>4</v>
@@ -1217,7 +1217,7 @@
         <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1574,7 +1574,7 @@
         <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>4</v>
@@ -1690,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -1949,7 +1949,7 @@
         <v>3</v>
       </c>
       <c r="AN11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2916,7 +2916,7 @@
         <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
         <v>2</v>
@@ -3288,7 +3288,7 @@
         <v>4</v>
       </c>
       <c r="AM22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN22" t="n">
         <v>3</v>
@@ -3526,10 +3526,10 @@
         <v>3</v>
       </c>
       <c r="AK24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM24" t="n">
         <v>4</v>
@@ -3645,7 +3645,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
         <v>3</v>
@@ -3654,7 +3654,7 @@
         <v>3</v>
       </c>
       <c r="AM25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN25" t="n">
         <v>3</v>
@@ -3892,13 +3892,13 @@
         <v>3</v>
       </c>
       <c r="AK27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL27" t="n">
         <v>4</v>
       </c>
       <c r="AM27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN27" t="n">
         <v>3</v>
@@ -4868,16 +4868,16 @@
         <v>4</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM35" t="n">
         <v>2</v>
       </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -5728,7 +5728,7 @@
         <v>5</v>
       </c>
       <c r="AM42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN42" t="n">
         <v>4</v>
@@ -6204,7 +6204,7 @@
         <v>4</v>
       </c>
       <c r="AI46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ46" t="n">
         <v>3</v>
@@ -6213,7 +6213,7 @@
         <v>3</v>
       </c>
       <c r="AL46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM46" t="n">
         <v>4</v>
@@ -6341,7 +6341,7 @@
         <v>3</v>
       </c>
       <c r="AN47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -6454,7 +6454,7 @@
         <v>4</v>
       </c>
       <c r="AK48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL48" t="n">
         <v>2</v>
@@ -6939,7 +6939,7 @@
         <v>2</v>
       </c>
       <c r="AJ52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK52" t="n">
         <v>4</v>
@@ -7073,7 +7073,7 @@
         <v>5</v>
       </c>
       <c r="AN53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -7683,7 +7683,7 @@
         <v>2</v>
       </c>
       <c r="AN58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -7921,13 +7921,13 @@
         <v>2</v>
       </c>
       <c r="AL60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -8159,13 +8159,13 @@
         <v>2</v>
       </c>
       <c r="AJ62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM62" t="n">
         <v>2</v>
@@ -8775,10 +8775,10 @@
         <v>4</v>
       </c>
       <c r="AL67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN67" t="n">
         <v>3</v>
@@ -8900,7 +8900,7 @@
         <v>4</v>
       </c>
       <c r="AM68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN68" t="n">
         <v>2</v>
@@ -9147,7 +9147,7 @@
         <v>2</v>
       </c>
       <c r="AN70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -9989,16 +9989,16 @@
         <v>4</v>
       </c>
       <c r="AJ77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL77" t="n">
         <v>3</v>
       </c>
       <c r="AM77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN77" t="n">
         <v>4</v>
@@ -10355,7 +10355,7 @@
         <v>3</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK80" t="n">
         <v>4</v>
@@ -10724,7 +10724,7 @@
         <v>5</v>
       </c>
       <c r="AK83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL83" t="n">
         <v>3</v>
@@ -10849,7 +10849,7 @@
         <v>3</v>
       </c>
       <c r="AL84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM84" t="n">
         <v>2</v>
@@ -11090,7 +11090,7 @@
         <v>3</v>
       </c>
       <c r="AK86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL86" t="n">
         <v>3</v>
@@ -11462,7 +11462,7 @@
         <v>2</v>
       </c>
       <c r="AM89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN89" t="n">
         <v>3</v>
@@ -11950,7 +11950,7 @@
         <v>1</v>
       </c>
       <c r="AM93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN93" t="n">
         <v>1</v>
@@ -12066,7 +12066,7 @@
         <v>2</v>
       </c>
       <c r="AK94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL94" t="n">
         <v>2</v>
@@ -12438,7 +12438,7 @@
         <v>2</v>
       </c>
       <c r="AM97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN97" t="n">
         <v>2</v>
@@ -13161,7 +13161,7 @@
         <v>2</v>
       </c>
       <c r="AJ103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK103" t="n">
         <v>4</v>
@@ -13411,7 +13411,7 @@
         <v>3</v>
       </c>
       <c r="AL105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM105" t="n">
         <v>4</v>
@@ -14146,7 +14146,7 @@
         <v>3</v>
       </c>
       <c r="AM111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN111" t="n">
         <v>4</v>
@@ -14387,7 +14387,7 @@
         <v>5</v>
       </c>
       <c r="AL113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM113" t="n">
         <v>5</v>
@@ -15000,7 +15000,7 @@
         <v>3</v>
       </c>
       <c r="AM118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN118" t="n">
         <v>3</v>
@@ -15110,7 +15110,7 @@
         <v>3</v>
       </c>
       <c r="AI119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ119" t="n">
         <v>2</v>
@@ -15119,7 +15119,7 @@
         <v>1</v>
       </c>
       <c r="AL119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM119" t="n">
         <v>2</v>
@@ -15726,7 +15726,7 @@
         <v>2</v>
       </c>
       <c r="AK124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL124" t="n">
         <v>2</v>
@@ -15976,10 +15976,10 @@
         <v>2</v>
       </c>
       <c r="AM126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -16214,7 +16214,7 @@
         <v>4</v>
       </c>
       <c r="AK128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL128" t="n">
         <v>4</v>
@@ -16467,7 +16467,7 @@
         <v>2</v>
       </c>
       <c r="AN130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -17556,7 +17556,7 @@
         <v>3</v>
       </c>
       <c r="AK139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL139" t="n">
         <v>3</v>
@@ -17684,7 +17684,7 @@
         <v>2</v>
       </c>
       <c r="AM140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN140" t="n">
         <v>1</v>
@@ -18169,7 +18169,7 @@
         <v>4</v>
       </c>
       <c r="AL144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM144" t="n">
         <v>4</v>
@@ -18285,19 +18285,19 @@
         <v>2</v>
       </c>
       <c r="AJ145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -18895,7 +18895,7 @@
         <v>1</v>
       </c>
       <c r="AJ150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK150" t="n">
         <v>3</v>
@@ -19639,7 +19639,7 @@
         <v>3</v>
       </c>
       <c r="AN156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -19880,7 +19880,7 @@
         <v>2</v>
       </c>
       <c r="AM158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN158" t="n">
         <v>3</v>
@@ -20243,7 +20243,7 @@
         <v>2</v>
       </c>
       <c r="AL161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM161" t="n">
         <v>2</v>
@@ -20493,7 +20493,7 @@
         <v>4</v>
       </c>
       <c r="AN163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -20609,7 +20609,7 @@
         <v>1</v>
       </c>
       <c r="AL164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM164" t="n">
         <v>3</v>
@@ -20728,7 +20728,7 @@
         <v>5</v>
       </c>
       <c r="AK165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL165" t="n">
         <v>5</v>
@@ -20856,7 +20856,7 @@
         <v>2</v>
       </c>
       <c r="AM166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN166" t="n">
         <v>3</v>
@@ -21091,7 +21091,7 @@
         <v>3</v>
       </c>
       <c r="AJ168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK168" t="n">
         <v>2</v>
@@ -21213,7 +21213,7 @@
         <v>3</v>
       </c>
       <c r="AJ169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK169" t="n">
         <v>1</v>
@@ -21335,7 +21335,7 @@
         <v>3</v>
       </c>
       <c r="AJ170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK170" t="n">
         <v>3</v>
@@ -21460,7 +21460,7 @@
         <v>3</v>
       </c>
       <c r="AK171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL171" t="n">
         <v>2</v>
@@ -22201,7 +22201,7 @@
         <v>3</v>
       </c>
       <c r="AN177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -22317,7 +22317,7 @@
         <v>3</v>
       </c>
       <c r="AL178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM178" t="n">
         <v>4</v>
@@ -23046,7 +23046,7 @@
         <v>1</v>
       </c>
       <c r="AK184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL184" t="n">
         <v>3</v>
@@ -23177,7 +23177,7 @@
         <v>2</v>
       </c>
       <c r="AN185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -23284,7 +23284,7 @@
         <v>4</v>
       </c>
       <c r="AI186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ186" t="n">
         <v>2</v>
@@ -23296,7 +23296,7 @@
         <v>3</v>
       </c>
       <c r="AM186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN186" t="n">
         <v>2</v>
@@ -23415,7 +23415,7 @@
         <v>3</v>
       </c>
       <c r="AL187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM187" t="n">
         <v>2</v>
@@ -23534,7 +23534,7 @@
         <v>1</v>
       </c>
       <c r="AK188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL188" t="n">
         <v>1</v>
@@ -23775,7 +23775,7 @@
         <v>3</v>
       </c>
       <c r="AJ190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK190" t="n">
         <v>3</v>
@@ -24144,7 +24144,7 @@
         <v>4</v>
       </c>
       <c r="AK193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL193" t="n">
         <v>2</v>
@@ -24391,7 +24391,7 @@
         <v>3</v>
       </c>
       <c r="AL195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM195" t="n">
         <v>2</v>
@@ -24757,7 +24757,7 @@
         <v>3</v>
       </c>
       <c r="AL198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM198" t="n">
         <v>1</v>
@@ -24876,16 +24876,16 @@
         <v>2</v>
       </c>
       <c r="AK199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL199" t="n">
         <v>1</v>
       </c>
       <c r="AM199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
@@ -25126,10 +25126,10 @@
         <v>1</v>
       </c>
       <c r="AM201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
@@ -25248,7 +25248,7 @@
         <v>4</v>
       </c>
       <c r="AM202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN202" t="n">
         <v>3</v>
@@ -25733,7 +25733,7 @@
         <v>3</v>
       </c>
       <c r="AL206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM206" t="n">
         <v>4</v>
@@ -25855,7 +25855,7 @@
         <v>4</v>
       </c>
       <c r="AL207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM207" t="n">
         <v>5</v>
@@ -26215,7 +26215,7 @@
         <v>2</v>
       </c>
       <c r="AJ210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK210" t="n">
         <v>1</v>
@@ -26459,19 +26459,19 @@
         <v>2</v>
       </c>
       <c r="AJ212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK212" t="n">
         <v>1</v>
       </c>
       <c r="AL212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM212" t="n">
         <v>1</v>
       </c>
       <c r="AN212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213">
@@ -26828,7 +26828,7 @@
         <v>1</v>
       </c>
       <c r="AK215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL215" t="n">
         <v>2</v>
@@ -27069,13 +27069,13 @@
         <v>1</v>
       </c>
       <c r="AJ217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK217" t="n">
         <v>3</v>
       </c>
       <c r="AL217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM217" t="n">
         <v>3</v>
@@ -27203,7 +27203,7 @@
         <v>4</v>
       </c>
       <c r="AN218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -27566,7 +27566,7 @@
         <v>2</v>
       </c>
       <c r="AM221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN221" t="n">
         <v>2</v>
@@ -28533,7 +28533,7 @@
         <v>4</v>
       </c>
       <c r="AJ229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK229" t="n">
         <v>1</v>
@@ -28545,7 +28545,7 @@
         <v>3</v>
       </c>
       <c r="AN229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -28783,10 +28783,10 @@
         <v>2</v>
       </c>
       <c r="AL231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM231" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN231" t="n">
         <v>2</v>
@@ -29387,7 +29387,7 @@
         <v>2</v>
       </c>
       <c r="AJ236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK236" t="n">
         <v>3</v>
@@ -29396,7 +29396,7 @@
         <v>2</v>
       </c>
       <c r="AM236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN236" t="n">
         <v>3</v>
@@ -29515,13 +29515,13 @@
         <v>2</v>
       </c>
       <c r="AL237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -29631,7 +29631,7 @@
         <v>2</v>
       </c>
       <c r="AJ238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK238" t="n">
         <v>1</v>
@@ -29753,13 +29753,13 @@
         <v>5</v>
       </c>
       <c r="AJ239" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM239" t="n">
         <v>3</v>
@@ -30485,13 +30485,13 @@
         <v>2</v>
       </c>
       <c r="AJ245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK245" t="n">
         <v>1</v>
       </c>
       <c r="AL245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM245" t="n">
         <v>2</v>
@@ -30610,7 +30610,7 @@
         <v>3</v>
       </c>
       <c r="AK246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL246" t="n">
         <v>2</v>
@@ -30851,7 +30851,7 @@
         <v>2</v>
       </c>
       <c r="AJ248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK248" t="n">
         <v>4</v>
@@ -31223,7 +31223,7 @@
         <v>3</v>
       </c>
       <c r="AL251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM251" t="n">
         <v>3</v>
@@ -31351,7 +31351,7 @@
         <v>5</v>
       </c>
       <c r="AN252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -31714,7 +31714,7 @@
         <v>2</v>
       </c>
       <c r="AM255" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN255" t="n">
         <v>4</v>
@@ -31836,10 +31836,10 @@
         <v>3</v>
       </c>
       <c r="AM256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="257">
@@ -31958,7 +31958,7 @@
         <v>3</v>
       </c>
       <c r="AM257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN257" t="n">
         <v>5</v>
@@ -32440,7 +32440,7 @@
         <v>4</v>
       </c>
       <c r="AK261" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL261" t="n">
         <v>3</v>
@@ -32565,7 +32565,7 @@
         <v>2</v>
       </c>
       <c r="AL262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM262" t="n">
         <v>2</v>
@@ -32928,7 +32928,7 @@
         <v>3</v>
       </c>
       <c r="AK265" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL265" t="n">
         <v>3</v>
@@ -33056,7 +33056,7 @@
         <v>1</v>
       </c>
       <c r="AM266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN266" t="n">
         <v>1</v>
@@ -33291,7 +33291,7 @@
         <v>2</v>
       </c>
       <c r="AJ268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK268" t="n">
         <v>1</v>
@@ -34035,7 +34035,7 @@
         <v>4</v>
       </c>
       <c r="AN274" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="275">
@@ -34398,7 +34398,7 @@
         <v>4</v>
       </c>
       <c r="AM277" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN277" t="n">
         <v>4</v>
@@ -34520,7 +34520,7 @@
         <v>2</v>
       </c>
       <c r="AM278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN278" t="n">
         <v>2</v>
@@ -34630,7 +34630,7 @@
         <v>4</v>
       </c>
       <c r="AI279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ279" t="n">
         <v>3</v>
@@ -34642,7 +34642,7 @@
         <v>2</v>
       </c>
       <c r="AM279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN279" t="n">
         <v>5</v>
@@ -35255,7 +35255,7 @@
         <v>2</v>
       </c>
       <c r="AN284" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="285">
@@ -35609,7 +35609,7 @@
         <v>3</v>
       </c>
       <c r="AJ287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK287" t="n">
         <v>3</v>
@@ -35621,7 +35621,7 @@
         <v>3</v>
       </c>
       <c r="AN287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288">
@@ -35856,7 +35856,7 @@
         <v>2</v>
       </c>
       <c r="AK289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL289" t="n">
         <v>2</v>
@@ -35981,7 +35981,7 @@
         <v>3</v>
       </c>
       <c r="AL290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM290" t="n">
         <v>4</v>
@@ -36472,7 +36472,7 @@
         <v>2</v>
       </c>
       <c r="AM294" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN294" t="n">
         <v>3</v>
@@ -36957,7 +36957,7 @@
         <v>3</v>
       </c>
       <c r="AL298" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM298" t="n">
         <v>2</v>
@@ -37076,13 +37076,13 @@
         <v>3</v>
       </c>
       <c r="AK299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL299" t="n">
         <v>2</v>
       </c>
       <c r="AM299" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN299" t="n">
         <v>4</v>
@@ -37326,7 +37326,7 @@
         <v>3</v>
       </c>
       <c r="AM301" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN301" t="n">
         <v>3</v>
@@ -37442,7 +37442,7 @@
         <v>2</v>
       </c>
       <c r="AK302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL302" t="n">
         <v>2</v>
@@ -37564,7 +37564,7 @@
         <v>2</v>
       </c>
       <c r="AK303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL303" t="n">
         <v>2</v>
@@ -37695,7 +37695,7 @@
         <v>4</v>
       </c>
       <c r="AN304" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="305">
@@ -38418,7 +38418,7 @@
         <v>4</v>
       </c>
       <c r="AK310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL310" t="n">
         <v>3</v>
@@ -38662,7 +38662,7 @@
         <v>4</v>
       </c>
       <c r="AK312" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL312" t="n">
         <v>4</v>
@@ -38781,7 +38781,7 @@
         <v>2</v>
       </c>
       <c r="AJ313" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK313" t="n">
         <v>3</v>
@@ -39031,7 +39031,7 @@
         <v>2</v>
       </c>
       <c r="AL315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM315" t="n">
         <v>3</v>
@@ -40370,16 +40370,16 @@
         <v>4</v>
       </c>
       <c r="AK326" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL326" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM326" t="n">
         <v>4</v>
       </c>
       <c r="AN326" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327">
@@ -40492,7 +40492,7 @@
         <v>3</v>
       </c>
       <c r="AK327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL327" t="n">
         <v>2</v>
@@ -40739,7 +40739,7 @@
         <v>4</v>
       </c>
       <c r="AL329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM329" t="n">
         <v>3</v>
@@ -41099,7 +41099,7 @@
         <v>1</v>
       </c>
       <c r="AJ332" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK332" t="n">
         <v>3</v>
@@ -41224,7 +41224,7 @@
         <v>3</v>
       </c>
       <c r="AK333" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL333" t="n">
         <v>2</v>
@@ -41346,7 +41346,7 @@
         <v>2</v>
       </c>
       <c r="AK334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL334" t="n">
         <v>2</v>
@@ -42325,13 +42325,13 @@
         <v>4</v>
       </c>
       <c r="AL342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM342" t="n">
         <v>3</v>
       </c>
       <c r="AN342" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -42441,7 +42441,7 @@
         <v>2</v>
       </c>
       <c r="AJ343" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK343" t="n">
         <v>3</v>
@@ -42569,7 +42569,7 @@
         <v>2</v>
       </c>
       <c r="AL344" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM344" t="n">
         <v>4</v>
@@ -42816,7 +42816,7 @@
         <v>1</v>
       </c>
       <c r="AM346" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN346" t="n">
         <v>2</v>
@@ -43914,7 +43914,7 @@
         <v>3</v>
       </c>
       <c r="AM355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN355" t="n">
         <v>4</v>
@@ -44036,7 +44036,7 @@
         <v>2</v>
       </c>
       <c r="AM356" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN356" t="n">
         <v>3</v>
@@ -44640,16 +44640,16 @@
         <v>1</v>
       </c>
       <c r="AK361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL361" t="n">
         <v>3</v>
       </c>
       <c r="AM361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -45009,10 +45009,10 @@
         <v>1</v>
       </c>
       <c r="AL364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN364" t="n">
         <v>2</v>
@@ -45369,7 +45369,7 @@
         <v>2</v>
       </c>
       <c r="AJ367" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK367" t="n">
         <v>5</v>
@@ -45854,10 +45854,10 @@
         <v>1</v>
       </c>
       <c r="AI371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ371" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK371" t="n">
         <v>3</v>
@@ -45991,7 +45991,7 @@
         <v>4</v>
       </c>
       <c r="AN372" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="373">
@@ -46226,7 +46226,7 @@
         <v>4</v>
       </c>
       <c r="AK374" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL374" t="n">
         <v>2</v>
@@ -46357,7 +46357,7 @@
         <v>3</v>
       </c>
       <c r="AN375" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376">
@@ -46592,7 +46592,7 @@
         <v>4</v>
       </c>
       <c r="AK377" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL377" t="n">
         <v>4</v>
@@ -46601,7 +46601,7 @@
         <v>4</v>
       </c>
       <c r="AN377" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="378">
@@ -47199,7 +47199,7 @@
         <v>2</v>
       </c>
       <c r="AJ382" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK382" t="n">
         <v>3</v>
@@ -47208,7 +47208,7 @@
         <v>3</v>
       </c>
       <c r="AM382" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN382" t="n">
         <v>3</v>
@@ -47333,7 +47333,7 @@
         <v>2</v>
       </c>
       <c r="AN383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -47812,7 +47812,7 @@
         <v>2</v>
       </c>
       <c r="AK387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL387" t="n">
         <v>1</v>
@@ -47928,7 +47928,7 @@
         <v>2</v>
       </c>
       <c r="AI388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ388" t="n">
         <v>3</v>
@@ -47940,10 +47940,10 @@
         <v>1</v>
       </c>
       <c r="AM388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -48178,7 +48178,7 @@
         <v>3</v>
       </c>
       <c r="AK390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL390" t="n">
         <v>3</v>
@@ -48431,7 +48431,7 @@
         <v>2</v>
       </c>
       <c r="AN392" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="393">
@@ -48919,7 +48919,7 @@
         <v>4</v>
       </c>
       <c r="AN396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -49276,7 +49276,7 @@
         <v>4</v>
       </c>
       <c r="AK399" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL399" t="n">
         <v>3</v>
@@ -49285,7 +49285,7 @@
         <v>5</v>
       </c>
       <c r="AN399" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="400">
@@ -49520,7 +49520,7 @@
         <v>1</v>
       </c>
       <c r="AK401" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL401" t="n">
         <v>1</v>
@@ -49761,7 +49761,7 @@
         <v>1</v>
       </c>
       <c r="AJ403" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK403" t="n">
         <v>4</v>
@@ -50130,16 +50130,16 @@
         <v>2</v>
       </c>
       <c r="AK406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM406" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN406" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="407">
@@ -50371,7 +50371,7 @@
         <v>2</v>
       </c>
       <c r="AJ408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK408" t="n">
         <v>3</v>
@@ -50618,7 +50618,7 @@
         <v>4</v>
       </c>
       <c r="AK410" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL410" t="n">
         <v>3</v>
@@ -50981,7 +50981,7 @@
         <v>4</v>
       </c>
       <c r="AJ413" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK413" t="n">
         <v>3</v>
@@ -50993,7 +50993,7 @@
         <v>4</v>
       </c>
       <c r="AN413" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="414">
@@ -51106,7 +51106,7 @@
         <v>3</v>
       </c>
       <c r="AK414" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL414" t="n">
         <v>3</v>
@@ -51716,7 +51716,7 @@
         <v>2</v>
       </c>
       <c r="AK419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL419" t="n">
         <v>2</v>
@@ -51960,7 +51960,7 @@
         <v>2</v>
       </c>
       <c r="AK421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL421" t="n">
         <v>1</v>
@@ -52567,7 +52567,7 @@
         <v>1</v>
       </c>
       <c r="AJ426" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK426" t="n">
         <v>5</v>
@@ -52576,10 +52576,10 @@
         <v>4</v>
       </c>
       <c r="AM426" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN426" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
@@ -52811,7 +52811,7 @@
         <v>1</v>
       </c>
       <c r="AJ428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK428" t="n">
         <v>2</v>
@@ -52820,7 +52820,7 @@
         <v>1</v>
       </c>
       <c r="AM428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN428" t="n">
         <v>1</v>
@@ -52933,7 +52933,7 @@
         <v>4</v>
       </c>
       <c r="AJ429" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK429" t="n">
         <v>2</v>
@@ -53555,7 +53555,7 @@
         <v>3</v>
       </c>
       <c r="AN434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -53799,7 +53799,7 @@
         <v>3</v>
       </c>
       <c r="AN436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -54034,7 +54034,7 @@
         <v>2</v>
       </c>
       <c r="AK438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL438" t="n">
         <v>2</v>
@@ -54287,7 +54287,7 @@
         <v>2</v>
       </c>
       <c r="AN440" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="441">
@@ -54406,7 +54406,7 @@
         <v>1</v>
       </c>
       <c r="AM441" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN441" t="n">
         <v>1</v>
@@ -55795,7 +55795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -56064,6 +56064,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>تذکر: میانگین گویه‌ها فقط برای توصیف است؛ تحلیل مقاله‌ها بر پایهٔ مدل متغیر پنهان (بدون نمرهٔ ترکیبی) انجام شده است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>قواعد: گویهٔ معکوس ندارد. حداقل ۸۰٪ گویه‌های هر سازه باید پاسخ داده شده باشد، وگرنه نمرهٔ سازه گم‌شده است. نمرهٔ بالاتر یعنی شدت بیشتر سازه (در کیفیت تصمیم: کیفیت بهتر).</t>
         </is>
@@ -70810,7 +70817,7 @@
         <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -70888,7 +70895,7 @@
         <v>1.4</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
@@ -70966,7 +70973,7 @@
         <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -70989,7 +70996,7 @@
         <v>3.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
         <v>1.2</v>
@@ -71044,7 +71051,7 @@
         <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
@@ -71252,7 +71259,7 @@
         <v>2.8</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -71330,7 +71337,7 @@
         <v>2.8</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="23">
@@ -71382,7 +71389,7 @@
         <v>2.4</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="25">
@@ -71408,7 +71415,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -71460,7 +71467,7 @@
         <v>2.2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="28">
@@ -71668,7 +71675,7 @@
         <v>3.4</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="36">
@@ -71850,7 +71857,7 @@
         <v>2.8</v>
       </c>
       <c r="H42" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="43">
@@ -71951,10 +71958,10 @@
         <v>4.25</v>
       </c>
       <c r="G46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" t="n">
         <v>3.2</v>
-      </c>
-      <c r="H46" t="n">
-        <v>3.4</v>
       </c>
     </row>
     <row r="47">
@@ -71980,7 +71987,7 @@
         <v>4.4</v>
       </c>
       <c r="H47" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -72006,7 +72013,7 @@
         <v>3.6</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="49">
@@ -72110,7 +72117,7 @@
         <v>1.8</v>
       </c>
       <c r="H52" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="53">
@@ -72136,7 +72143,7 @@
         <v>4</v>
       </c>
       <c r="H53" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="54">
@@ -72266,7 +72273,7 @@
         <v>2.2</v>
       </c>
       <c r="H58" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -72318,7 +72325,7 @@
         <v>3.6</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="61">
@@ -72370,7 +72377,7 @@
         <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="63">
@@ -72500,7 +72507,7 @@
         <v>2.6</v>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="68">
@@ -72526,7 +72533,7 @@
         <v>1.4</v>
       </c>
       <c r="H68" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="69">
@@ -72578,7 +72585,7 @@
         <v>2.2</v>
       </c>
       <c r="H70" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -72760,7 +72767,7 @@
         <v>4.6</v>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="78">
@@ -72838,7 +72845,7 @@
         <v>3</v>
       </c>
       <c r="H80" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="81">
@@ -72916,7 +72923,7 @@
         <v>2.8</v>
       </c>
       <c r="H83" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="84">
@@ -72942,7 +72949,7 @@
         <v>2.6</v>
       </c>
       <c r="H84" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="85">
@@ -72994,7 +73001,7 @@
         <v>1.2</v>
       </c>
       <c r="H86" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="87">
@@ -73072,7 +73079,7 @@
         <v>3.8</v>
       </c>
       <c r="H89" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="90">
@@ -73176,7 +73183,7 @@
         <v>4.4</v>
       </c>
       <c r="H93" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="94">
@@ -73202,7 +73209,7 @@
         <v>3</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="95">
@@ -73280,7 +73287,7 @@
         <v>2</v>
       </c>
       <c r="H97" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="98">
@@ -73436,7 +73443,7 @@
         <v>1.6</v>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="104">
@@ -73488,7 +73495,7 @@
         <v>2.8</v>
       </c>
       <c r="H105" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="106">
@@ -73644,7 +73651,7 @@
         <v>2.8</v>
       </c>
       <c r="H111" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="112">
@@ -73696,7 +73703,7 @@
         <v>4.2</v>
       </c>
       <c r="H113" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
@@ -73826,7 +73833,7 @@
         <v>1.2</v>
       </c>
       <c r="H118" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="119">
@@ -73849,10 +73856,10 @@
         <v>3.5</v>
       </c>
       <c r="G119" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="H119" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="120">
@@ -73982,7 +73989,7 @@
         <v>4</v>
       </c>
       <c r="H124" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="125">
@@ -74034,7 +74041,7 @@
         <v>2.6</v>
       </c>
       <c r="H126" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -74086,7 +74093,7 @@
         <v>3.4</v>
       </c>
       <c r="H128" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="129">
@@ -74138,7 +74145,7 @@
         <v>1.4</v>
       </c>
       <c r="H130" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="131">
@@ -74372,7 +74379,7 @@
         <v>4</v>
       </c>
       <c r="H139" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="140">
@@ -74398,7 +74405,7 @@
         <v>2.2</v>
       </c>
       <c r="H140" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="141">
@@ -74502,7 +74509,7 @@
         <v>3.2</v>
       </c>
       <c r="H144" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -74528,7 +74535,7 @@
         <v>3.2</v>
       </c>
       <c r="H145" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="146">
@@ -74658,7 +74665,7 @@
         <v>1.6</v>
       </c>
       <c r="H150" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="151">
@@ -74814,7 +74821,7 @@
         <v>2.2</v>
       </c>
       <c r="H156" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="157">
@@ -74866,7 +74873,7 @@
         <v>3.4</v>
       </c>
       <c r="H158" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="159">
@@ -74944,7 +74951,7 @@
         <v>1.6</v>
       </c>
       <c r="H161" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -74996,7 +75003,7 @@
         <v>4</v>
       </c>
       <c r="H163" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="164">
@@ -75022,7 +75029,7 @@
         <v>2.2</v>
       </c>
       <c r="H164" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="165">
@@ -75048,7 +75055,7 @@
         <v>3</v>
       </c>
       <c r="H165" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="166">
@@ -75074,7 +75081,7 @@
         <v>1.6</v>
       </c>
       <c r="H166" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="167">
@@ -75126,7 +75133,7 @@
         <v>2.8</v>
       </c>
       <c r="H168" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="169">
@@ -75152,7 +75159,7 @@
         <v>3.2</v>
       </c>
       <c r="H169" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -75178,7 +75185,7 @@
         <v>2.6</v>
       </c>
       <c r="H170" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="171">
@@ -75204,7 +75211,7 @@
         <v>2.6</v>
       </c>
       <c r="H171" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -75360,7 +75367,7 @@
         <v>2.6</v>
       </c>
       <c r="H177" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -75386,7 +75393,7 @@
         <v>3.4</v>
       </c>
       <c r="H178" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="179">
@@ -75542,7 +75549,7 @@
         <v>1.6</v>
       </c>
       <c r="H184" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="185">
@@ -75568,7 +75575,7 @@
         <v>3.2</v>
       </c>
       <c r="H185" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="186">
@@ -75591,10 +75598,10 @@
         <v>3.75</v>
       </c>
       <c r="G186" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H186" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="187">
@@ -75620,7 +75627,7 @@
         <v>1.2</v>
       </c>
       <c r="H187" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="188">
@@ -75646,7 +75653,7 @@
         <v>1.8</v>
       </c>
       <c r="H188" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="189">
@@ -75698,7 +75705,7 @@
         <v>2.8</v>
       </c>
       <c r="H190" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="191">
@@ -75776,7 +75783,7 @@
         <v>1.8</v>
       </c>
       <c r="H193" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
@@ -75828,7 +75835,7 @@
         <v>1.6</v>
       </c>
       <c r="H195" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="196">
@@ -75906,7 +75913,7 @@
         <v>4.2</v>
       </c>
       <c r="H198" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="199">
@@ -75932,7 +75939,7 @@
         <v>1.8</v>
       </c>
       <c r="H199" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="200">
@@ -75984,7 +75991,7 @@
         <v>1.6</v>
       </c>
       <c r="H201" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="202">
@@ -76010,7 +76017,7 @@
         <v>1.4</v>
       </c>
       <c r="H202" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="203">
@@ -76114,7 +76121,7 @@
         <v>3</v>
       </c>
       <c r="H206" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="207">
@@ -76140,7 +76147,7 @@
         <v>1.6</v>
       </c>
       <c r="H207" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="208">
@@ -76218,7 +76225,7 @@
         <v>1.8</v>
       </c>
       <c r="H210" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="211">
@@ -76270,7 +76277,7 @@
         <v>2</v>
       </c>
       <c r="H212" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -76348,7 +76355,7 @@
         <v>3</v>
       </c>
       <c r="H215" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="216">
@@ -76400,7 +76407,7 @@
         <v>2</v>
       </c>
       <c r="H217" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218">
@@ -76426,7 +76433,7 @@
         <v>2.6</v>
       </c>
       <c r="H218" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="219">
@@ -76504,7 +76511,7 @@
         <v>1.4</v>
       </c>
       <c r="H221" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
@@ -76712,7 +76719,7 @@
         <v>4.4</v>
       </c>
       <c r="H229" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="230">
@@ -76764,7 +76771,7 @@
         <v>3</v>
       </c>
       <c r="H231" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="232">
@@ -76894,7 +76901,7 @@
         <v>3.6</v>
       </c>
       <c r="H236" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="237">
@@ -76920,7 +76927,7 @@
         <v>2.2</v>
       </c>
       <c r="H237" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="238">
@@ -76946,7 +76953,7 @@
         <v>2.4</v>
       </c>
       <c r="H238" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -76972,7 +76979,7 @@
         <v>4.6</v>
       </c>
       <c r="H239" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -77128,7 +77135,7 @@
         <v>2.4</v>
       </c>
       <c r="H245" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
@@ -77154,7 +77161,7 @@
         <v>3.4</v>
       </c>
       <c r="H246" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247">
@@ -77206,7 +77213,7 @@
         <v>2.4</v>
       </c>
       <c r="H248" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249">
@@ -77284,7 +77291,7 @@
         <v>1.2</v>
       </c>
       <c r="H251" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="252">
@@ -77310,7 +77317,7 @@
         <v>3.4</v>
       </c>
       <c r="H252" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="253">
@@ -77388,7 +77395,7 @@
         <v>2</v>
       </c>
       <c r="H255" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -77414,7 +77421,7 @@
         <v>2</v>
       </c>
       <c r="H256" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -77440,7 +77447,7 @@
         <v>2.2</v>
       </c>
       <c r="H257" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="258">
@@ -77544,7 +77551,7 @@
         <v>3.8</v>
       </c>
       <c r="H261" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="262">
@@ -77570,7 +77577,7 @@
         <v>2.4</v>
       </c>
       <c r="H262" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="263">
@@ -77648,7 +77655,7 @@
         <v>3.6</v>
       </c>
       <c r="H265" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266">
@@ -77674,7 +77681,7 @@
         <v>1.8</v>
       </c>
       <c r="H266" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -77726,7 +77733,7 @@
         <v>3.2</v>
       </c>
       <c r="H268" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="269">
@@ -77882,7 +77889,7 @@
         <v>4.2</v>
       </c>
       <c r="H274" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="275">
@@ -77960,7 +77967,7 @@
         <v>3</v>
       </c>
       <c r="H277" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="278">
@@ -77986,7 +77993,7 @@
         <v>2.6</v>
       </c>
       <c r="H278" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="279">
@@ -78009,10 +78016,10 @@
         <v>1.75</v>
       </c>
       <c r="G279" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H279" t="n">
         <v>3.4</v>
-      </c>
-      <c r="H279" t="n">
-        <v>3.2</v>
       </c>
     </row>
     <row r="280">
@@ -78142,7 +78149,7 @@
         <v>2.8</v>
       </c>
       <c r="H284" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="285">
@@ -78220,7 +78227,7 @@
         <v>2.2</v>
       </c>
       <c r="H287" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="288">
@@ -78272,7 +78279,7 @@
         <v>2</v>
       </c>
       <c r="H289" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="290">
@@ -78298,7 +78305,7 @@
         <v>1.4</v>
       </c>
       <c r="H290" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="291">
@@ -78402,7 +78409,7 @@
         <v>3</v>
       </c>
       <c r="H294" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
@@ -78506,7 +78513,7 @@
         <v>3.4</v>
       </c>
       <c r="H298" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -78532,7 +78539,7 @@
         <v>2.2</v>
       </c>
       <c r="H299" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -78584,7 +78591,7 @@
         <v>2</v>
       </c>
       <c r="H301" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="302">
@@ -78610,7 +78617,7 @@
         <v>3.6</v>
       </c>
       <c r="H302" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -78636,7 +78643,7 @@
         <v>3.8</v>
       </c>
       <c r="H303" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="304">
@@ -78662,7 +78669,7 @@
         <v>1.8</v>
       </c>
       <c r="H304" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="305">
@@ -78818,7 +78825,7 @@
         <v>2.6</v>
       </c>
       <c r="H310" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="311">
@@ -78870,7 +78877,7 @@
         <v>3.6</v>
       </c>
       <c r="H312" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="313">
@@ -78896,7 +78903,7 @@
         <v>2.6</v>
       </c>
       <c r="H313" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="314">
@@ -78948,7 +78955,7 @@
         <v>2.8</v>
       </c>
       <c r="H315" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="316">
@@ -79234,7 +79241,7 @@
         <v>1.6</v>
       </c>
       <c r="H326" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="327">
@@ -79260,7 +79267,7 @@
         <v>4.4</v>
       </c>
       <c r="H327" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="328">
@@ -79312,7 +79319,7 @@
         <v>3.6</v>
       </c>
       <c r="H329" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="330">
@@ -79390,7 +79397,7 @@
         <v>1.6</v>
       </c>
       <c r="H332" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="333">
@@ -79416,7 +79423,7 @@
         <v>2</v>
       </c>
       <c r="H333" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -79442,7 +79449,7 @@
         <v>2.2</v>
       </c>
       <c r="H334" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="335">
@@ -79650,7 +79657,7 @@
         <v>3.6</v>
       </c>
       <c r="H342" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -79676,7 +79683,7 @@
         <v>2.6</v>
       </c>
       <c r="H343" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="344">
@@ -79702,7 +79709,7 @@
         <v>4.2</v>
       </c>
       <c r="H344" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -79754,7 +79761,7 @@
         <v>2.4</v>
       </c>
       <c r="H346" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347">
@@ -79988,7 +79995,7 @@
         <v>3.4</v>
       </c>
       <c r="H355" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -80014,7 +80021,7 @@
         <v>3</v>
       </c>
       <c r="H356" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="357">
@@ -80144,7 +80151,7 @@
         <v>1.4</v>
       </c>
       <c r="H361" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="362">
@@ -80222,7 +80229,7 @@
         <v>1.2</v>
       </c>
       <c r="H364" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="365">
@@ -80300,7 +80307,7 @@
         <v>2</v>
       </c>
       <c r="H367" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="368">
@@ -80401,10 +80408,10 @@
         <v>2.5</v>
       </c>
       <c r="G371" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="H371" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="372">
@@ -80430,7 +80437,7 @@
         <v>2</v>
       </c>
       <c r="H372" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="373">
@@ -80482,7 +80489,7 @@
         <v>1.6</v>
       </c>
       <c r="H374" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="375">
@@ -80508,7 +80515,7 @@
         <v>3</v>
       </c>
       <c r="H375" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376">
@@ -80560,7 +80567,7 @@
         <v>3.4</v>
       </c>
       <c r="H377" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="378">
@@ -80690,7 +80697,7 @@
         <v>4.4</v>
       </c>
       <c r="H382" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="383">
@@ -80716,7 +80723,7 @@
         <v>1.4</v>
       </c>
       <c r="H383" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="384">
@@ -80820,7 +80827,7 @@
         <v>1.2</v>
       </c>
       <c r="H387" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="388">
@@ -80843,10 +80850,10 @@
         <v>1.75</v>
       </c>
       <c r="G388" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="H388" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="389">
@@ -80898,7 +80905,7 @@
         <v>3.8</v>
       </c>
       <c r="H390" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="391">
@@ -80950,7 +80957,7 @@
         <v>1.2</v>
       </c>
       <c r="H392" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="393">
@@ -81054,7 +81061,7 @@
         <v>3</v>
       </c>
       <c r="H396" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="397">
@@ -81132,7 +81139,7 @@
         <v>3.6</v>
       </c>
       <c r="H399" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="400">
@@ -81184,7 +81191,7 @@
         <v>2.6</v>
       </c>
       <c r="H401" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="402">
@@ -81236,7 +81243,7 @@
         <v>2.2</v>
       </c>
       <c r="H403" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="404">
@@ -81314,7 +81321,7 @@
         <v>2</v>
       </c>
       <c r="H406" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="407">
@@ -81366,7 +81373,7 @@
         <v>3</v>
       </c>
       <c r="H408" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -81418,7 +81425,7 @@
         <v>3.2</v>
       </c>
       <c r="H410" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="411">
@@ -81496,7 +81503,7 @@
         <v>3.4</v>
       </c>
       <c r="H413" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="414">
@@ -81522,7 +81529,7 @@
         <v>2.2</v>
       </c>
       <c r="H414" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="415">
@@ -81652,7 +81659,7 @@
         <v>3.8</v>
       </c>
       <c r="H419" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="420">
@@ -81704,7 +81711,7 @@
         <v>1.8</v>
       </c>
       <c r="H421" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="422">
@@ -81834,7 +81841,7 @@
         <v>3.4</v>
       </c>
       <c r="H426" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="427">
@@ -81886,7 +81893,7 @@
         <v>2</v>
       </c>
       <c r="H428" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="429">
@@ -81912,7 +81919,7 @@
         <v>4.2</v>
       </c>
       <c r="H429" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="430">
@@ -82042,7 +82049,7 @@
         <v>2</v>
       </c>
       <c r="H434" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="435">
@@ -82094,7 +82101,7 @@
         <v>3.4</v>
       </c>
       <c r="H436" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -82146,7 +82153,7 @@
         <v>1.4</v>
       </c>
       <c r="H438" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="439">
@@ -82198,7 +82205,7 @@
         <v>3</v>
       </c>
       <c r="H440" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="441">
@@ -82224,7 +82231,7 @@
         <v>1.8</v>
       </c>
       <c r="H441" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="442">
@@ -83021,10 +83028,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.344</v>
+        <v>2.346</v>
       </c>
       <c r="C29" t="n">
-        <v>1.056</v>
+        <v>1.058</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -83033,10 +83040,10 @@
         <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>0.414</v>
+        <v>0.413</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.518</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="30">
@@ -83046,10 +83053,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.821</v>
+        <v>2.817</v>
       </c>
       <c r="C30" t="n">
-        <v>1.04</v>
+        <v>1.037</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -83058,10 +83065,10 @@
         <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.047</v>
+        <v>-0.02</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.513</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="31">
@@ -83071,10 +83078,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.667</v>
+        <v>2.665</v>
       </c>
       <c r="C31" t="n">
-        <v>1.069</v>
+        <v>1.039</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -83083,10 +83090,10 @@
         <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.179</v>
+        <v>0.144</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.528</v>
+        <v>-0.462</v>
       </c>
     </row>
     <row r="32">
@@ -83096,10 +83103,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.505</v>
+        <v>2.511</v>
       </c>
       <c r="C32" t="n">
-        <v>1.017</v>
+        <v>1.006</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -83108,10 +83115,10 @@
         <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>0.111</v>
+        <v>0.143</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.651</v>
+        <v>-0.604</v>
       </c>
     </row>
     <row r="33">
@@ -83121,10 +83128,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.12</v>
+        <v>3.131</v>
       </c>
       <c r="C33" t="n">
-        <v>1.089</v>
+        <v>1.099</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
@@ -83133,10 +83140,10 @@
         <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.049</v>
+        <v>-0.128</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.72</v>
+        <v>-0.667</v>
       </c>
     </row>
     <row r="34">
@@ -83146,10 +83153,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.846</v>
+        <v>2.869</v>
       </c>
       <c r="C34" t="n">
-        <v>1.066</v>
+        <v>1.069</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -83158,10 +83165,10 @@
         <v>5</v>
       </c>
       <c r="F34" t="n">
-        <v>0.107</v>
+        <v>0.029</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.582</v>
       </c>
     </row>
   </sheetData>
@@ -83274,7 +83281,7 @@
         <v>0.83</v>
       </c>
       <c r="E3" t="n">
-        <v>0.551</v>
+        <v>0.552</v>
       </c>
       <c r="F3" t="n">
         <v>0.743</v>
@@ -83283,7 +83290,7 @@
         <v>0.637</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -83308,7 +83315,7 @@
         <v>0.698</v>
       </c>
       <c r="G4" t="n">
-        <v>0.599</v>
+        <v>0.598</v>
       </c>
       <c r="H4" t="n">
         <v>0.763</v>
@@ -83327,7 +83334,7 @@
         <v>0.856</v>
       </c>
       <c r="D5" t="n">
-        <v>0.858</v>
+        <v>0.859</v>
       </c>
       <c r="E5" t="n">
         <v>0.505</v>
@@ -83339,7 +83346,7 @@
         <v>0.633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.836</v>
+        <v>0.835</v>
       </c>
     </row>
     <row r="6">
@@ -83358,7 +83365,7 @@
         <v>0.842</v>
       </c>
       <c r="E6" t="n">
-        <v>0.573</v>
+        <v>0.574</v>
       </c>
       <c r="F6" t="n">
         <v>0.757</v>
@@ -83392,7 +83399,7 @@
         <v>0.728</v>
       </c>
       <c r="G7" t="n">
-        <v>0.596</v>
+        <v>0.597</v>
       </c>
       <c r="H7" t="n">
         <v>0.829</v>
@@ -83408,22 +83415,22 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D8" t="n">
         <v>0.842</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.844</v>
-      </c>
       <c r="E8" t="n">
-        <v>0.52</v>
+        <v>0.516</v>
       </c>
       <c r="F8" t="n">
-        <v>0.721</v>
+        <v>0.719</v>
       </c>
       <c r="G8" t="n">
-        <v>0.653</v>
+        <v>0.641</v>
       </c>
       <c r="H8" t="n">
-        <v>0.773</v>
+        <v>0.764</v>
       </c>
     </row>
   </sheetData>
@@ -83487,16 +83494,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2756</v>
+        <v>0.275</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2715</v>
+        <v>0.271</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0533</v>
+        <v>0.0534</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1653</v>
+        <v>5.1535</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -83509,16 +83516,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2392</v>
+        <v>0.2388</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2332</v>
+        <v>0.2329</v>
       </c>
       <c r="D3" t="n">
         <v>0.0538</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4463</v>
+        <v>4.4374</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -83531,16 +83538,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3854</v>
+        <v>0.3846</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3566</v>
+        <v>0.3561</v>
       </c>
       <c r="D4" t="n">
         <v>0.0552</v>
       </c>
       <c r="E4" t="n">
-        <v>6.9828</v>
+        <v>6.9701</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -83553,7 +83560,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3712</v>
+        <v>0.3711</v>
       </c>
       <c r="C5" t="n">
         <v>0.202</v>
@@ -83562,7 +83569,7 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7736</v>
+        <v>4.7704</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -83575,16 +83582,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4861</v>
+        <v>0.4837</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5019</v>
+        <v>0.5</v>
       </c>
       <c r="D6" t="n">
         <v>0.0508</v>
       </c>
       <c r="E6" t="n">
-        <v>9.5702</v>
+        <v>9.5281</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -83597,16 +83604,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.2698</v>
+        <v>-0.2696</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2416</v>
+        <v>-0.2419</v>
       </c>
       <c r="D7" t="n">
         <v>0.0562</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.7982</v>
+        <v>-4.7962</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -83619,19 +83626,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0344</v>
+        <v>-0.029</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0181</v>
+        <v>-0.0153</v>
       </c>
       <c r="D8" t="n">
         <v>0.08359999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4116</v>
+        <v>-0.3474</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6806</v>
+        <v>0.7282999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -83641,16 +83648,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3021</v>
+        <v>-0.3235</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3574</v>
+        <v>-0.3753</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0458</v>
+        <v>0.0472</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.5916</v>
+        <v>-6.8476</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -83663,16 +83670,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2845</v>
+        <v>0.263</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3477</v>
+        <v>0.3149</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0531</v>
+        <v>0.0541</v>
       </c>
       <c r="E10" t="n">
-        <v>5.3572</v>
+        <v>4.865</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -83685,19 +83692,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.029</v>
+        <v>0.016</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0366</v>
+        <v>0.0198</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0486</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5964</v>
+        <v>0.3208</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.7483</v>
       </c>
     </row>
     <row r="12">
@@ -83707,19 +83714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.134</v>
+        <v>0.1108</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0863</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0738</v>
+        <v>0.0759</v>
       </c>
       <c r="E12" t="n">
-        <v>1.816</v>
+        <v>1.4596</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0694</v>
+        <v>0.1444</v>
       </c>
     </row>
     <row r="13">
@@ -83729,19 +83736,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0393</v>
+        <v>0.0418</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0517</v>
+        <v>0.054</v>
       </c>
       <c r="D13" t="n">
-        <v>0.035</v>
+        <v>0.0361</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1206</v>
+        <v>1.1576</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2624</v>
+        <v>0.247</v>
       </c>
     </row>
   </sheetData>
